--- a/sampleprojects/TaxReturn/excel/states/KS.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/KS.xlsx
@@ -82,7 +82,7 @@
     <t>MFJ/QSS: $8,000 std ded, 5.58%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 8000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0558</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 8000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0558</t>
   </si>
   <si>
     <t>X</t>
@@ -91,13 +91,13 @@
     <t>HOH: $6,000 std ded, 5.58%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 6000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0558</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 6000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0558</t>
   </si>
   <si>
     <t>Default (Single/MFS): $3,500 std ded, 5.58%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 3500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0558</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 3500.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0558</t>
   </si>
   <si>
     <t>Policy:</t>
